--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/164.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/164.xlsx
@@ -426,13 +426,13 @@
         <v>-15.22866068256664</v>
       </c>
       <c r="E2">
-        <v>-6.56127636710313</v>
+        <v>-4.673074787916882</v>
       </c>
       <c r="F2">
-        <v>-3.569180977117918</v>
+        <v>-3.723553869568828</v>
       </c>
       <c r="G2">
-        <v>-2.543473425217151</v>
+        <v>-1.281728514380263</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.04197372215281</v>
       </c>
       <c r="E3">
-        <v>-6.866395888791943</v>
+        <v>-6.015540907490759</v>
       </c>
       <c r="F3">
-        <v>-4.571235486732007</v>
+        <v>-4.186085234432975</v>
       </c>
       <c r="G3">
-        <v>-2.115588724811889</v>
+        <v>-1.34801556771309</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.7128158326337</v>
       </c>
       <c r="E4">
-        <v>-7.018670355773866</v>
+        <v>-5.135341414619871</v>
       </c>
       <c r="F4">
-        <v>-3.617396930165266</v>
+        <v>-4.098068712783318</v>
       </c>
       <c r="G4">
-        <v>-2.262080364924639</v>
+        <v>-1.674700201528371</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.25334138478879</v>
       </c>
       <c r="E5">
-        <v>-8.72654809997468</v>
+        <v>-6.448472079572061</v>
       </c>
       <c r="F5">
-        <v>-3.816672306052326</v>
+        <v>-4.247728194712299</v>
       </c>
       <c r="G5">
-        <v>-1.163442722262104</v>
+        <v>-1.155593418788492</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.69102357636888</v>
       </c>
       <c r="E6">
-        <v>-8.447168424545465</v>
+        <v>-8.782601551241624</v>
       </c>
       <c r="F6">
-        <v>-3.635342681579515</v>
+        <v>-3.990012326925137</v>
       </c>
       <c r="G6">
-        <v>-1.122699838310293</v>
+        <v>-0.4817285637243022</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.05252798770286</v>
       </c>
       <c r="E7">
-        <v>-8.908683324563182</v>
+        <v>-8.056315832943437</v>
       </c>
       <c r="F7">
-        <v>-4.070464197452428</v>
+        <v>-3.95635493098199</v>
       </c>
       <c r="G7">
-        <v>-1.447351797164461</v>
+        <v>-0.8142629315074751</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.35520498214712</v>
       </c>
       <c r="E8">
-        <v>-11.92812941018354</v>
+        <v>-9.973812110485303</v>
       </c>
       <c r="F8">
-        <v>-3.902802635125808</v>
+        <v>-3.758696528265194</v>
       </c>
       <c r="G8">
-        <v>-1.68996843755549</v>
+        <v>-0.6056025567127514</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.61273159978438</v>
       </c>
       <c r="E9">
-        <v>-11.02621588444587</v>
+        <v>-11.1324448277178</v>
       </c>
       <c r="F9">
-        <v>-4.253570670004244</v>
+        <v>-4.140820754441801</v>
       </c>
       <c r="G9">
-        <v>-1.003311634527556</v>
+        <v>-0.3000756194389528</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.85689215703482</v>
       </c>
       <c r="E10">
-        <v>-11.44211546578432</v>
+        <v>-11.38479404179523</v>
       </c>
       <c r="F10">
-        <v>-3.919784166883197</v>
+        <v>-3.983730816909708</v>
       </c>
       <c r="G10">
-        <v>0.144401535209136</v>
+        <v>-0.02433366038197714</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.1064623184028</v>
       </c>
       <c r="E11">
-        <v>-13.5463569544545</v>
+        <v>-12.29600452467065</v>
       </c>
       <c r="F11">
-        <v>-3.891298268635728</v>
+        <v>-4.027813216617087</v>
       </c>
       <c r="G11">
-        <v>0.2822294776456133</v>
+        <v>0.2839741351448092</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.373835336087305</v>
       </c>
       <c r="E12">
-        <v>-13.83892354619405</v>
+        <v>-13.19250652396915</v>
       </c>
       <c r="F12">
-        <v>-3.564348281689986</v>
+        <v>-4.15157047822793</v>
       </c>
       <c r="G12">
-        <v>0.2256621860160866</v>
+        <v>0.4838814275336999</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.666797173715088</v>
       </c>
       <c r="E13">
-        <v>-15.61747718423258</v>
+        <v>-14.19203583541616</v>
       </c>
       <c r="F13">
-        <v>-4.146881090360682</v>
+        <v>-3.903804131315792</v>
       </c>
       <c r="G13">
-        <v>0.7137226726886806</v>
+        <v>1.622911036320884</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.014944632034023</v>
       </c>
       <c r="E14">
-        <v>-16.11413304254982</v>
+        <v>-15.27944018498201</v>
       </c>
       <c r="F14">
-        <v>-4.307525552418188</v>
+        <v>-3.390762235698544</v>
       </c>
       <c r="G14">
-        <v>2.14171324887115</v>
+        <v>2.277445615981269</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.4326825274513</v>
       </c>
       <c r="E15">
-        <v>-17.11335441776431</v>
+        <v>-15.57043086776689</v>
       </c>
       <c r="F15">
-        <v>-3.973058959659442</v>
+        <v>-3.568835547910951</v>
       </c>
       <c r="G15">
-        <v>2.542481270764241</v>
+        <v>3.353647691524164</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.927985496217685</v>
       </c>
       <c r="E16">
-        <v>-17.07394310847555</v>
+        <v>-16.67786918634268</v>
       </c>
       <c r="F16">
-        <v>-3.421337276535874</v>
+        <v>-3.32118682917001</v>
       </c>
       <c r="G16">
-        <v>2.030720588576005</v>
+        <v>2.963380720081641</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.506901401244082</v>
       </c>
       <c r="E17">
-        <v>-18.5694807064567</v>
+        <v>-17.89195759627311</v>
       </c>
       <c r="F17">
-        <v>-3.577052124179319</v>
+        <v>-3.269022048713517</v>
       </c>
       <c r="G17">
-        <v>4.722607930195889</v>
+        <v>4.093842637013191</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.184948775447809</v>
       </c>
       <c r="E18">
-        <v>-19.37620570855314</v>
+        <v>-19.0354108686319</v>
       </c>
       <c r="F18">
-        <v>-3.276064000004716</v>
+        <v>-2.730846657727929</v>
       </c>
       <c r="G18">
-        <v>3.656122305810754</v>
+        <v>4.716122571484457</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.95993849275415</v>
       </c>
       <c r="E19">
-        <v>-18.93844265470565</v>
+        <v>-20.00214949978936</v>
       </c>
       <c r="F19">
-        <v>-2.612762884458859</v>
+        <v>-3.19354535280744</v>
       </c>
       <c r="G19">
-        <v>4.562890660653751</v>
+        <v>4.420239253366555</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.817938830888319</v>
       </c>
       <c r="E20">
-        <v>-21.46566625806228</v>
+        <v>-20.67577812232636</v>
       </c>
       <c r="F20">
-        <v>-2.805767519106727</v>
+        <v>-2.499493582534861</v>
       </c>
       <c r="G20">
-        <v>4.872062508566287</v>
+        <v>5.841876892659163</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.746901963714475</v>
       </c>
       <c r="E21">
-        <v>-21.46819314655856</v>
+        <v>-22.17899601222452</v>
       </c>
       <c r="F21">
-        <v>-2.75665527252955</v>
+        <v>-2.341551254945287</v>
       </c>
       <c r="G21">
-        <v>4.913113273253249</v>
+        <v>5.875303470969184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.739780738328264</v>
       </c>
       <c r="E22">
-        <v>-22.23432943612424</v>
+        <v>-21.82641355446131</v>
       </c>
       <c r="F22">
-        <v>-2.549628034487092</v>
+        <v>-2.129434527580029</v>
       </c>
       <c r="G22">
-        <v>4.894067704765822</v>
+        <v>6.163824135807746</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.780694973528193</v>
       </c>
       <c r="E23">
-        <v>-21.84508898126895</v>
+        <v>-22.24436000605123</v>
       </c>
       <c r="F23">
-        <v>-2.248962145232178</v>
+        <v>-1.554936054349085</v>
       </c>
       <c r="G23">
-        <v>5.468043469273582</v>
+        <v>5.645833006914602</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.84814526303288</v>
       </c>
       <c r="E24">
-        <v>-23.76556952318187</v>
+        <v>-22.75594624317176</v>
       </c>
       <c r="F24">
-        <v>-1.863208841463907</v>
+        <v>-2.28393498861097</v>
       </c>
       <c r="G24">
-        <v>5.136250663691206</v>
+        <v>6.153054931168498</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.933283450916698</v>
       </c>
       <c r="E25">
-        <v>-24.70854725122109</v>
+        <v>-23.77122105874344</v>
       </c>
       <c r="F25">
-        <v>-1.607330292576154</v>
+        <v>-1.462124113804623</v>
       </c>
       <c r="G25">
-        <v>5.075472358135726</v>
+        <v>6.446915505961904</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.031453797262877</v>
       </c>
       <c r="E26">
-        <v>-24.83282216341359</v>
+        <v>-22.87666177479423</v>
       </c>
       <c r="F26">
-        <v>-1.696499901650506</v>
+        <v>-1.807711538945951</v>
       </c>
       <c r="G26">
-        <v>5.389775551634132</v>
+        <v>6.260131216090685</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.135930064413232</v>
       </c>
       <c r="E27">
-        <v>-23.02292695676798</v>
+        <v>-23.36812800189868</v>
       </c>
       <c r="F27">
-        <v>-1.26220592481299</v>
+        <v>-1.669643402084344</v>
       </c>
       <c r="G27">
-        <v>4.527676387752523</v>
+        <v>6.288191400081548</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.235988831657531</v>
       </c>
       <c r="E28">
-        <v>-24.17589002454287</v>
+        <v>-22.87808371563264</v>
       </c>
       <c r="F28">
-        <v>-1.44645554438067</v>
+        <v>-1.872387152286926</v>
       </c>
       <c r="G28">
-        <v>4.223185651232516</v>
+        <v>5.584144301335822</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.335895140762498</v>
       </c>
       <c r="E29">
-        <v>-24.83901258738207</v>
+        <v>-22.4206263283258</v>
       </c>
       <c r="F29">
-        <v>-1.457680751056006</v>
+        <v>-1.711968834530385</v>
       </c>
       <c r="G29">
-        <v>4.812164808124253</v>
+        <v>6.230442243694501</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.440012581929389</v>
       </c>
       <c r="E30">
-        <v>-24.18638702729265</v>
+        <v>-22.48768397143138</v>
       </c>
       <c r="F30">
-        <v>-1.125286733539065</v>
+        <v>-1.756676651626877</v>
       </c>
       <c r="G30">
-        <v>4.463398835562034</v>
+        <v>5.311130231803206</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.54989269993446</v>
       </c>
       <c r="E31">
-        <v>-23.47551170604257</v>
+        <v>-21.74154089460956</v>
       </c>
       <c r="F31">
-        <v>-1.489793241792932</v>
+        <v>-1.249856623572055</v>
       </c>
       <c r="G31">
-        <v>4.002024656481504</v>
+        <v>4.606560066862277</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.660944514111037</v>
       </c>
       <c r="E32">
-        <v>-22.99179369796524</v>
+        <v>-21.57213068198261</v>
       </c>
       <c r="F32">
-        <v>-1.21793962754219</v>
+        <v>-1.664789169103938</v>
       </c>
       <c r="G32">
-        <v>4.678829275984567</v>
+        <v>5.092753405850722</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.781695333887577</v>
       </c>
       <c r="E33">
-        <v>-22.11325162658116</v>
+        <v>-21.83812871671916</v>
       </c>
       <c r="F33">
-        <v>-1.598624979540134</v>
+        <v>-1.847208925078835</v>
       </c>
       <c r="G33">
-        <v>4.283023761854843</v>
+        <v>5.03984095649655</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.916707380068627</v>
       </c>
       <c r="E34">
-        <v>-22.00928239183906</v>
+        <v>-20.55152132402989</v>
       </c>
       <c r="F34">
-        <v>-1.425656067263777</v>
+        <v>-1.870610304207921</v>
       </c>
       <c r="G34">
-        <v>4.18292610692944</v>
+        <v>4.712934516130138</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.065648986440804</v>
       </c>
       <c r="E35">
-        <v>-21.41167326246882</v>
+        <v>-20.30362812837601</v>
       </c>
       <c r="F35">
-        <v>-1.313556420112531</v>
+        <v>-1.654514099839614</v>
       </c>
       <c r="G35">
-        <v>3.008470350326514</v>
+        <v>4.596654914608777</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.22113474170133</v>
       </c>
       <c r="E36">
-        <v>-20.61020129022129</v>
+        <v>-20.23016722302358</v>
       </c>
       <c r="F36">
-        <v>-1.754961931103082</v>
+        <v>-1.609573511502935</v>
       </c>
       <c r="G36">
-        <v>4.709620660045328</v>
+        <v>3.895047687925495</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.388428734653478</v>
       </c>
       <c r="E37">
-        <v>-19.44373431295552</v>
+        <v>-18.45386876504088</v>
       </c>
       <c r="F37">
-        <v>-1.32605482748597</v>
+        <v>-1.487121756918903</v>
       </c>
       <c r="G37">
-        <v>2.972964749417831</v>
+        <v>3.767661206119879</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.567260826811374</v>
       </c>
       <c r="E38">
-        <v>-18.70542096769296</v>
+        <v>-18.6238540938668</v>
       </c>
       <c r="F38">
-        <v>-1.566123156123892</v>
+        <v>-1.229188028504804</v>
       </c>
       <c r="G38">
-        <v>2.436275659318882</v>
+        <v>3.859621540109754</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.752326969090266</v>
       </c>
       <c r="E39">
-        <v>-19.24236665925644</v>
+        <v>-17.58019933168905</v>
       </c>
       <c r="F39">
-        <v>-1.434271088252892</v>
+        <v>-0.7921869469949394</v>
       </c>
       <c r="G39">
-        <v>3.121998888504741</v>
+        <v>3.948519619475804</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.934638016689862</v>
       </c>
       <c r="E40">
-        <v>-17.69414479467005</v>
+        <v>-16.73752277444572</v>
       </c>
       <c r="F40">
-        <v>-2.120875007206902</v>
+        <v>-1.258888313364778</v>
       </c>
       <c r="G40">
-        <v>2.716582860674513</v>
+        <v>3.511885147210248</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.120228155306622</v>
       </c>
       <c r="E41">
-        <v>-16.4006360075931</v>
+        <v>-14.9717847178489</v>
       </c>
       <c r="F41">
-        <v>-1.179381610044081</v>
+        <v>-1.301455629092436</v>
       </c>
       <c r="G41">
-        <v>2.40335559447637</v>
+        <v>3.354634234094867</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.310041608272654</v>
       </c>
       <c r="E42">
-        <v>-16.46780233407486</v>
+        <v>-15.09533507420017</v>
       </c>
       <c r="F42">
-        <v>-1.634425361954323</v>
+        <v>-1.27458339054562</v>
       </c>
       <c r="G42">
-        <v>2.437305238981596</v>
+        <v>3.121399679762133</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.500579762551085</v>
       </c>
       <c r="E43">
-        <v>-16.21423496048937</v>
+        <v>-15.2113636352247</v>
       </c>
       <c r="F43">
-        <v>-1.685895142159867</v>
+        <v>-1.038458919112427</v>
       </c>
       <c r="G43">
-        <v>2.845369703243241</v>
+        <v>3.155574441364029</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.686904667760835</v>
       </c>
       <c r="E44">
-        <v>-14.41028111174182</v>
+        <v>-14.11009309824736</v>
       </c>
       <c r="F44">
-        <v>-0.7847283269001326</v>
+        <v>-1.024963157386017</v>
       </c>
       <c r="G44">
-        <v>2.34167019944313</v>
+        <v>2.529712496619272</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.878952319737076</v>
       </c>
       <c r="E45">
-        <v>-13.84707479940786</v>
+        <v>-12.69521215081683</v>
       </c>
       <c r="F45">
-        <v>-1.347357951983765</v>
+        <v>-0.9752495160744077</v>
       </c>
       <c r="G45">
-        <v>2.490528879616459</v>
+        <v>2.853963879463189</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.079388044479476</v>
       </c>
       <c r="E46">
-        <v>-13.27372923377072</v>
+        <v>-10.803713842553</v>
       </c>
       <c r="F46">
-        <v>-1.144389714215025</v>
+        <v>-0.7340405255228308</v>
       </c>
       <c r="G46">
-        <v>2.582161469597946</v>
+        <v>2.847081255287044</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.283787752249886</v>
       </c>
       <c r="E47">
-        <v>-11.89742182793753</v>
+        <v>-11.55103432261681</v>
       </c>
       <c r="F47">
-        <v>-0.759255200896645</v>
+        <v>-0.7678130645349667</v>
       </c>
       <c r="G47">
-        <v>2.262273385774789</v>
+        <v>2.042489577968114</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.488725349848051</v>
       </c>
       <c r="E48">
-        <v>-12.51765974192409</v>
+        <v>-9.995118580691393</v>
       </c>
       <c r="F48">
-        <v>-0.7863734645620925</v>
+        <v>-0.9324626829850077</v>
       </c>
       <c r="G48">
-        <v>2.377308222173384</v>
+        <v>1.596072443634012</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.703745151001391</v>
       </c>
       <c r="E49">
-        <v>-10.97199193667803</v>
+        <v>-8.707831916900979</v>
       </c>
       <c r="F49">
-        <v>-0.8864849786600238</v>
+        <v>-1.025794838258428</v>
       </c>
       <c r="G49">
-        <v>2.278571201464621</v>
+        <v>2.416879173004292</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.92953823588253</v>
       </c>
       <c r="E50">
-        <v>-8.98161892693072</v>
+        <v>-6.916005321545971</v>
       </c>
       <c r="F50">
-        <v>-0.9927247548038661</v>
+        <v>-0.7047072074222975</v>
       </c>
       <c r="G50">
-        <v>1.927421636114126</v>
+        <v>1.716619338355494</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.15778505624817</v>
       </c>
       <c r="E51">
-        <v>-9.847073708432633</v>
+        <v>-8.165116949451724</v>
       </c>
       <c r="F51">
-        <v>-1.294489059234892</v>
+        <v>-0.9237010409655972</v>
       </c>
       <c r="G51">
-        <v>1.862558117363186</v>
+        <v>1.068056982847954</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.3854310196694</v>
       </c>
       <c r="E52">
-        <v>-7.252887559924584</v>
+        <v>-6.894368272737323</v>
       </c>
       <c r="F52">
-        <v>-0.7668587852869416</v>
+        <v>-0.5633272576842976</v>
       </c>
       <c r="G52">
-        <v>1.501711964128166</v>
+        <v>1.32249558135972</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.6175024695367</v>
       </c>
       <c r="E53">
-        <v>-6.828773326736218</v>
+        <v>-5.292040200707289</v>
       </c>
       <c r="F53">
-        <v>-0.7556882508601903</v>
+        <v>-0.4188434152880078</v>
       </c>
       <c r="G53">
-        <v>1.352121653390658</v>
+        <v>0.9749412684648736</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.84962991526181</v>
       </c>
       <c r="E54">
-        <v>-7.881398995923161</v>
+        <v>-4.716104347937765</v>
       </c>
       <c r="F54">
-        <v>-0.7987732962145982</v>
+        <v>-0.4861971404422328</v>
       </c>
       <c r="G54">
-        <v>0.7723656763713304</v>
+        <v>0.9266867566844568</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.06642448351947</v>
       </c>
       <c r="E55">
-        <v>-6.403608487578071</v>
+        <v>-4.84946337898965</v>
       </c>
       <c r="F55">
-        <v>-0.7937020309746596</v>
+        <v>-0.6963257860407722</v>
       </c>
       <c r="G55">
-        <v>-0.1005655925147748</v>
+        <v>0.2659382830468598</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.2636486796916</v>
       </c>
       <c r="E56">
-        <v>-6.178910135791475</v>
+        <v>-3.169096114385433</v>
       </c>
       <c r="F56">
-        <v>-0.9695122434426183</v>
+        <v>-0.6385015994883527</v>
       </c>
       <c r="G56">
-        <v>-0.05899176163260719</v>
+        <v>0.3333608534996568</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.44211422660552</v>
       </c>
       <c r="E57">
-        <v>-5.67052552979437</v>
+        <v>-2.693891637442529</v>
       </c>
       <c r="F57">
-        <v>-0.8274638012105591</v>
+        <v>-1.049459638221604</v>
       </c>
       <c r="G57">
-        <v>-0.856866342052356</v>
+        <v>0.5060091139181885</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.5962623327656</v>
       </c>
       <c r="E58">
-        <v>-4.570785617031624</v>
+        <v>-2.332786591596887</v>
       </c>
       <c r="F58">
-        <v>-0.8417050935994882</v>
+        <v>-0.3502794453582927</v>
       </c>
       <c r="G58">
-        <v>-0.7419606169297923</v>
+        <v>-0.05413188078095709</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.71064635836892</v>
       </c>
       <c r="E59">
-        <v>-3.740272540972895</v>
+        <v>-2.101630635875353</v>
       </c>
       <c r="F59">
-        <v>-1.386219151951299</v>
+        <v>-0.4623873761835666</v>
       </c>
       <c r="G59">
-        <v>-0.2248202982402402</v>
+        <v>0.2339749658651965</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.78761586487443</v>
       </c>
       <c r="E60">
-        <v>-2.844481512093599</v>
+        <v>-1.437430296222327</v>
       </c>
       <c r="F60">
-        <v>-0.9667430112150596</v>
+        <v>-0.6112416849970266</v>
       </c>
       <c r="G60">
-        <v>-0.8991519402254669</v>
+        <v>-0.298916928500208</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.83038413761991</v>
       </c>
       <c r="E61">
-        <v>-2.816083451591498</v>
+        <v>-0.4870077569144952</v>
       </c>
       <c r="F61">
-        <v>-0.8383253545960663</v>
+        <v>-0.8341189049246504</v>
       </c>
       <c r="G61">
-        <v>-0.3860306238205899</v>
+        <v>-0.2758391155459485</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.83655838221602</v>
       </c>
       <c r="E62">
-        <v>-2.541051111209647</v>
+        <v>0.2509161395834049</v>
       </c>
       <c r="F62">
-        <v>-1.024162954474913</v>
+        <v>-0.6489390287636264</v>
       </c>
       <c r="G62">
-        <v>-1.701681147673431</v>
+        <v>-0.5163899755204715</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.79450644446868</v>
       </c>
       <c r="E63">
-        <v>-4.033106312678899</v>
+        <v>-0.3942917800814523</v>
       </c>
       <c r="F63">
-        <v>-0.9645387255562101</v>
+        <v>-0.711353199094958</v>
       </c>
       <c r="G63">
-        <v>-0.4412439023245548</v>
+        <v>-0.6182720144915422</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.71155782189765</v>
       </c>
       <c r="E64">
-        <v>-3.215703168872377</v>
+        <v>0.9417665487715716</v>
       </c>
       <c r="F64">
-        <v>-0.5926713445610672</v>
+        <v>-0.8095901177603542</v>
       </c>
       <c r="G64">
-        <v>-0.9542791445454106</v>
+        <v>-0.4928983443738031</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.59301668372311</v>
       </c>
       <c r="E65">
-        <v>-2.346607494268297</v>
+        <v>-0.08973831764359777</v>
       </c>
       <c r="F65">
-        <v>-1.006799545344832</v>
+        <v>-0.7910355163050481</v>
       </c>
       <c r="G65">
-        <v>-1.294441009251064</v>
+        <v>-0.2571477754312234</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.43874701002032</v>
       </c>
       <c r="E66">
-        <v>-3.138705525319958</v>
+        <v>0.11654725882781</v>
       </c>
       <c r="F66">
-        <v>-1.192666138082777</v>
+        <v>-1.037302518218119</v>
       </c>
       <c r="G66">
-        <v>-0.2942854752907675</v>
+        <v>-0.01361411392581703</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.24112799298208</v>
       </c>
       <c r="E67">
-        <v>-1.124567083980397</v>
+        <v>0.0748445416911737</v>
       </c>
       <c r="F67">
-        <v>-0.6188229034674476</v>
+        <v>-0.9059002538468387</v>
       </c>
       <c r="G67">
-        <v>-1.008207931380138</v>
+        <v>-0.3851632608893009</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.00990883752874</v>
       </c>
       <c r="E68">
-        <v>-1.570508561885736</v>
+        <v>0.877593543608875</v>
       </c>
       <c r="F68">
-        <v>-1.290280952828671</v>
+        <v>-0.9486208175440148</v>
       </c>
       <c r="G68">
-        <v>-2.308010873736488</v>
+        <v>0.04105292456416808</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.7499051895273</v>
       </c>
       <c r="E69">
-        <v>-2.42596900125272</v>
+        <v>-0.3507505024977018</v>
       </c>
       <c r="F69">
-        <v>-1.24610908944179</v>
+        <v>-0.5152471568910086</v>
       </c>
       <c r="G69">
-        <v>-0.3620159264787168</v>
+        <v>0.5531446613063317</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.4603118764518</v>
       </c>
       <c r="E70">
-        <v>-1.116207520962238</v>
+        <v>-0.2788156928858582</v>
       </c>
       <c r="F70">
-        <v>-0.9148076885291417</v>
+        <v>-0.9411713094906389</v>
       </c>
       <c r="G70">
-        <v>-1.243163969393293</v>
+        <v>0.5433123410546962</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.13451138803397</v>
       </c>
       <c r="E71">
-        <v>-0.490856959821015</v>
+        <v>0.8075652215542606</v>
       </c>
       <c r="F71">
-        <v>-1.518024002880339</v>
+        <v>-0.7459110304049478</v>
       </c>
       <c r="G71">
-        <v>-1.452387136929693</v>
+        <v>1.132390814312611</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.782047499587497</v>
       </c>
       <c r="E72">
-        <v>-1.614910249530944</v>
+        <v>0.5716226688066196</v>
       </c>
       <c r="F72">
-        <v>-1.242425339601541</v>
+        <v>-1.051325121612709</v>
       </c>
       <c r="G72">
-        <v>-0.3755560577343359</v>
+        <v>0.635746083056687</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.405065725102711</v>
       </c>
       <c r="E73">
-        <v>-2.881144037659698</v>
+        <v>0.1517923720295084</v>
       </c>
       <c r="F73">
-        <v>-1.410876336063029</v>
+        <v>-0.9418530558631428</v>
       </c>
       <c r="G73">
-        <v>-0.7875104130046247</v>
+        <v>0.827343906142007</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.001209544008198</v>
       </c>
       <c r="E74">
-        <v>-3.017183925324123</v>
+        <v>0.573705766850148</v>
       </c>
       <c r="F74">
-        <v>-1.204164706001037</v>
+        <v>-1.179929160897332</v>
       </c>
       <c r="G74">
-        <v>0.272446815577067</v>
+        <v>2.016359442026646</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.564139607096736</v>
       </c>
       <c r="E75">
-        <v>-1.592761483159428</v>
+        <v>-0.1167053803592747</v>
       </c>
       <c r="F75">
-        <v>-1.682268549670411</v>
+        <v>-0.9744534550003173</v>
       </c>
       <c r="G75">
-        <v>0.39366906158856</v>
+        <v>2.340915395060176</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.103868121362995</v>
       </c>
       <c r="E76">
-        <v>-1.72766019537392</v>
+        <v>-0.1969589967232088</v>
       </c>
       <c r="F76">
-        <v>-1.311898028572127</v>
+        <v>-1.408330763034226</v>
       </c>
       <c r="G76">
-        <v>0.6410363348284424</v>
+        <v>2.202090978416378</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.623007022968909</v>
       </c>
       <c r="E77">
-        <v>-4.224597364567248</v>
+        <v>-2.747567639855446</v>
       </c>
       <c r="F77">
-        <v>-1.616800188724958</v>
+        <v>-1.651331512278058</v>
       </c>
       <c r="G77">
-        <v>0.8400928170137403</v>
+        <v>2.30473775340702</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.122429534490836</v>
       </c>
       <c r="E78">
-        <v>-5.371940596098625</v>
+        <v>-2.658501613072585</v>
       </c>
       <c r="F78">
-        <v>-1.309456001468674</v>
+        <v>-1.630654633536779</v>
       </c>
       <c r="G78">
-        <v>1.296352203236095</v>
+        <v>3.066822026001709</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.601632143654332</v>
       </c>
       <c r="E79">
-        <v>-5.791073507878555</v>
+        <v>-3.101988658065766</v>
       </c>
       <c r="F79">
-        <v>-1.619180916640603</v>
+        <v>-1.868220464250844</v>
       </c>
       <c r="G79">
-        <v>2.071370777252716</v>
+        <v>3.727712853097494</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.076947498194037</v>
       </c>
       <c r="E80">
-        <v>-6.301726879353502</v>
+        <v>-3.393853336334129</v>
       </c>
       <c r="F80">
-        <v>-1.730424031897354</v>
+        <v>-1.944481624087372</v>
       </c>
       <c r="G80">
-        <v>2.260386374817404</v>
+        <v>3.246733623333401</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.556995202468885</v>
       </c>
       <c r="E81">
-        <v>-7.145802735065203</v>
+        <v>-4.594655203526054</v>
       </c>
       <c r="F81">
-        <v>-1.882663878286056</v>
+        <v>-1.48604653603007</v>
       </c>
       <c r="G81">
-        <v>2.474595223935947</v>
+        <v>4.114215734261866</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.04923043334601</v>
       </c>
       <c r="E82">
-        <v>-8.45664199216951</v>
+        <v>-5.294422178035323</v>
       </c>
       <c r="F82">
-        <v>-1.732465957545255</v>
+        <v>-1.621906245395814</v>
       </c>
       <c r="G82">
-        <v>2.525415408509299</v>
+        <v>4.826201521210763</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.561600516285779</v>
       </c>
       <c r="E83">
-        <v>-9.536837011115152</v>
+        <v>-6.199745644700767</v>
       </c>
       <c r="F83">
-        <v>-1.938584476546842</v>
+        <v>-1.931469628924197</v>
       </c>
       <c r="G83">
-        <v>2.939786462023255</v>
+        <v>4.593284779249799</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.114508248617127</v>
       </c>
       <c r="E84">
-        <v>-11.31812584745431</v>
+        <v>-7.830720843303322</v>
       </c>
       <c r="F84">
-        <v>-2.105777182923478</v>
+        <v>-2.258734395483004</v>
       </c>
       <c r="G84">
-        <v>3.288251174941401</v>
+        <v>6.087069137479745</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.720186421172235</v>
       </c>
       <c r="E85">
-        <v>-11.31281847591732</v>
+        <v>-8.528010742530396</v>
       </c>
       <c r="F85">
-        <v>-2.261788586097126</v>
+        <v>-2.029731398611677</v>
       </c>
       <c r="G85">
-        <v>3.153111395482812</v>
+        <v>5.511871781667994</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.386507489819432</v>
       </c>
       <c r="E86">
-        <v>-11.6087089675785</v>
+        <v>-10.08135431121946</v>
       </c>
       <c r="F86">
-        <v>-1.791883094613258</v>
+        <v>-2.268115656319708</v>
       </c>
       <c r="G86">
-        <v>2.981737695096899</v>
+        <v>5.500063065729413</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.12358724470863</v>
       </c>
       <c r="E87">
-        <v>-12.6704595118909</v>
+        <v>-10.97673324896406</v>
       </c>
       <c r="F87">
-        <v>-2.732829769290231</v>
+        <v>-2.431417521005394</v>
       </c>
       <c r="G87">
-        <v>4.524312873484623</v>
+        <v>6.594840612293159</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.947105928171429</v>
       </c>
       <c r="E88">
-        <v>-14.12796245668163</v>
+        <v>-13.57560183959604</v>
       </c>
       <c r="F88">
-        <v>-2.671798972521574</v>
+        <v>-2.059843382070842</v>
       </c>
       <c r="G88">
-        <v>3.581181486438273</v>
+        <v>6.225185097378138</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.865094583092688</v>
       </c>
       <c r="E89">
-        <v>-15.78984449038654</v>
+        <v>-14.81873135333766</v>
       </c>
       <c r="F89">
-        <v>-2.640504080411212</v>
+        <v>-2.545387621752162</v>
       </c>
       <c r="G89">
-        <v>4.495557474930513</v>
+        <v>6.378559361667033</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.87703353483715</v>
       </c>
       <c r="E90">
-        <v>-16.7672703202021</v>
+        <v>-16.96795417432602</v>
       </c>
       <c r="F90">
-        <v>-2.373774746914188</v>
+        <v>-2.751183905834059</v>
       </c>
       <c r="G90">
-        <v>4.11646690522857</v>
+        <v>6.517767801593386</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.989083798708253</v>
       </c>
       <c r="E91">
-        <v>-18.83770222193101</v>
+        <v>-17.96402373163117</v>
       </c>
       <c r="F91">
-        <v>-2.080135069969819</v>
+        <v>-2.643266685699548</v>
       </c>
       <c r="G91">
-        <v>4.652500507310743</v>
+        <v>5.730318129076803</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.207564359194594</v>
       </c>
       <c r="E92">
-        <v>-22.13850692612194</v>
+        <v>-19.43379431250868</v>
       </c>
       <c r="F92">
-        <v>-2.607751261671922</v>
+        <v>-3.314185467881549</v>
       </c>
       <c r="G92">
-        <v>4.820898027256851</v>
+        <v>6.447564372887602</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.532246104236832</v>
       </c>
       <c r="E93">
-        <v>-24.03430275621905</v>
+        <v>-21.14197999294202</v>
       </c>
       <c r="F93">
-        <v>-2.688818609179493</v>
+        <v>-3.072854707321761</v>
       </c>
       <c r="G93">
-        <v>4.516420532919001</v>
+        <v>6.044492211299177</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.951308804399021</v>
       </c>
       <c r="E94">
-        <v>-25.45218155344266</v>
+        <v>-23.90361099635768</v>
       </c>
       <c r="F94">
-        <v>-3.171695505823798</v>
+        <v>-2.990279731141095</v>
       </c>
       <c r="G94">
-        <v>3.834666647834728</v>
+        <v>5.156057657652665</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.461917270718802</v>
       </c>
       <c r="E95">
-        <v>-26.91979658069252</v>
+        <v>-27.0090528033837</v>
       </c>
       <c r="F95">
-        <v>-3.076049720394358</v>
+        <v>-3.308471389537038</v>
       </c>
       <c r="G95">
-        <v>2.878369221178696</v>
+        <v>5.52537549692268</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.06214946281902</v>
       </c>
       <c r="E96">
-        <v>-30.52579779063039</v>
+        <v>-28.42650592405059</v>
       </c>
       <c r="F96">
-        <v>-3.040849904347199</v>
+        <v>-3.338270250117945</v>
       </c>
       <c r="G96">
-        <v>2.733297805102293</v>
+        <v>5.026582221611769</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.730496268926889</v>
       </c>
       <c r="E97">
-        <v>-32.48268952780198</v>
+        <v>-30.25343724991306</v>
       </c>
       <c r="F97">
-        <v>-3.703933159266119</v>
+        <v>-3.210989113575592</v>
       </c>
       <c r="G97">
-        <v>2.68548028533306</v>
+        <v>5.342964437708838</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.459447196951093</v>
       </c>
       <c r="E98">
-        <v>-35.70781211013971</v>
+        <v>-33.93833353401256</v>
       </c>
       <c r="F98">
-        <v>-3.491092438790814</v>
+        <v>-3.464162214525802</v>
       </c>
       <c r="G98">
-        <v>1.076038708143137</v>
+        <v>3.146841222231432</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.214254658140127</v>
       </c>
       <c r="E99">
-        <v>-38.20068270967415</v>
+        <v>-35.93661778785127</v>
       </c>
       <c r="F99">
-        <v>-3.619956585439916</v>
+        <v>-3.887569786955728</v>
       </c>
       <c r="G99">
-        <v>1.750241238852332</v>
+        <v>4.319476178787758</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.016056343207955</v>
       </c>
       <c r="E100">
-        <v>-39.07864287214824</v>
+        <v>-38.70779028600109</v>
       </c>
       <c r="F100">
-        <v>-3.909926594789884</v>
+        <v>-4.091401183558185</v>
       </c>
       <c r="G100">
-        <v>1.620881671905311</v>
+        <v>3.127812206471702</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.787164079818677</v>
       </c>
       <c r="E101">
-        <v>-42.46423419518478</v>
+        <v>-40.81924563376549</v>
       </c>
       <c r="F101">
-        <v>-3.92952576754012</v>
+        <v>-4.185192254372756</v>
       </c>
       <c r="G101">
-        <v>1.223056724996631</v>
+        <v>2.788269413781892</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.603833342635872</v>
       </c>
       <c r="E102">
-        <v>-43.13859416627402</v>
+        <v>-42.81959034327769</v>
       </c>
       <c r="F102">
-        <v>-4.356463013473374</v>
+        <v>-4.480077795890936</v>
       </c>
       <c r="G102">
-        <v>0.4811568485548797</v>
+        <v>2.593231933881269</v>
       </c>
     </row>
   </sheetData>
